--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,7 +776,6 @@
           <t>NSE:DRREDDY26AUG1180PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1133,6 +1132,279 @@
           <t>NSE:BOSCHLTD26AUG45000CE</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:27:35</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1187</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1190</v>
+      </c>
+      <c r="I8" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2331</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:DRREDDY26AUG1190PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:27:35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I9" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="M9" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1426</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="S9" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>75.61</v>
+      </c>
+      <c r="U9" t="n">
+        <v>36</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:NAUKRI26AUG1380CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:27:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>45655</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H10" t="n">
+        <v>45500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1217.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>853.41</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1543.43</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1738.72</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1999.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>41</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="U10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:BOSCHLTD26AUG45500CE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1399,12 +1399,11 @@
           <t>NSE:BOSCHLTD26AUG45500CE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:36:22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1399,11 +1399,7 @@
           <t>NSE:BOSCHLTD26AUG45500CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-11 12:36:22</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,7 +1399,101 @@
           <t>NSE:BOSCHLTD26AUG45500CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:55:24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1483.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1480</v>
+      </c>
+      <c r="I11" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="M11" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1351</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="S11" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="U11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:MFSL26AUG1480PE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1488,12 +1488,11 @@
           <t>NSE:MFSL26AUG1480PE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:14:17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1221,6 +1221,11 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:34:02</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1221,11 +1221,7 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-11 13:34:02</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1221,7 +1221,11 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:43:44</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1221,6 +1221,16 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:55:56</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-11 13:43:44</t>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,6 +1508,101 @@
           <t>2026-08-11 13:14:17</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:00:40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1171.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1170</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="S12" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>63.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:ZYDUSLIFE26AUG1170CE</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1597,12 +1597,11 @@
           <t>NSE:ZYDUSLIFE26AUG1170CE</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:07:42</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1597,6 +1597,16 @@
           <t>NSE:ZYDUSLIFE26AUG1170CE</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:23:23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-11 14:07:42</t>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1602,9 +1602,14 @@
           <t>2026-08-11 14:23:23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:24:23</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1607,9 +1607,14 @@
           <t>2026-08-11 14:24:23</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:31:22</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,101 @@
           <t>2026-08-11 14:07:42</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-11 15:11:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="H13" t="n">
+        <v>440</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4807</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="S13" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:VBL26AUG440PE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1711,12 +1711,11 @@
           <t>NSE:VBL26AUG440PE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-11 15:13:59</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -776,6 +776,16 @@
           <t>NSE:DRREDDY26AUG1180PE</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:33:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -865,6 +875,16 @@
           <t>NSE:NAUKRI26AUG1360CE</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:44:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -954,6 +974,16 @@
           <t>NSE:INDUSTOWER26AUG375PE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:37:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-11 11:53:25</t>
@@ -1048,6 +1078,16 @@
           <t>NSE:DIVISLAB26AUG8400CE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-11 15:13:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1132,6 +1172,16 @@
           <t>NSE:BOSCHLTD26AUG45000CE</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:26:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1501,6 +1551,16 @@
       <c r="W11" t="inlineStr">
         <is>
           <t>NSE:MFSL26AUG1480PE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:54:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
+++ b/backend/signal_logs/2026-08-11/signals_2026-08-11.xlsx
@@ -1375,6 +1375,11 @@
           <t>NSE:NAUKRI26AUG1380CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~27.65 (-21.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1464,6 +1469,11 @@
           <t>NSE:BOSCHLTD26AUG45500CE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed down ~885.25 (-27.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1769,6 +1779,11 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:VBL26AUG440PE</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed up ~10.8 (+3.9% from entry)</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
